--- a/frontend/public/ejemplos/efectivo_equivalentes/RQ-001_cuentas.xlsx
+++ b/frontend/public/ejemplos/efectivo_equivalentes/RQ-001_cuentas.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,50 +435,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Saldo según libros</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Saldo según estado bancario (o arqueo en caja)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Saldo confirmado por el banco</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Restringido (Sí/No)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Monto restringido</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Motivo de la restricción</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fin de la restricción</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Restringido ya presentado aparte (Sí/No)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Fecha de adquisición (inversiones)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fecha de vencimiento (inversiones)</t>
         </is>
@@ -502,15 +507,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -518,6 +527,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,15 +547,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>300.00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>300.00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -553,6 +567,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,26 +587,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>125680.50</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>131210.50</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>131210.50</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,46 +631,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>47700.00</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>45900.00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>45900.00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>10000.00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Garantía de préstamo (pignoración)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>30/06/2027</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -670,26 +695,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>22000.00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>22000.00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>21500.00</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -709,38 +739,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>1650.00</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1200.00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>1650.00</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Embargo judicial</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -760,26 +795,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>-3200.00</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>-3200.00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>-3200.00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -799,30 +839,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>50000.00</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>50000.00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>50000.00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>15/11/2025</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
@@ -846,30 +891,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>01/10/2025</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>

--- a/frontend/public/ejemplos/efectivo_equivalentes/RQ-001_cuentas.xlsx
+++ b/frontend/public/ejemplos/efectivo_equivalentes/RQ-001_cuentas.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léame" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,60 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F6B4C"/>
+    </font>
+    <font>
+      <color rgb="006B7280"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6B4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B7280"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +87,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,512 +492,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Código de cuenta</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Banco / caja y número de cuenta</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Tipo (Banco, Caja o Inversión)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Saldo anterior (cierre previo)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Saldo según libros</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Saldo según estado bancario (o arqueo en caja)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Saldo confirmado por el banco</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Restringido (Sí/No)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Monto restringido</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Motivo de la restricción</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Fin de la restricción</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Restringido ya presentado aparte (Sí/No)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Fecha de adquisición (inversiones)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Fecha de vencimiento (inversiones)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>1.1.01.01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Caja general</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Caja</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>1.1.01.02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Caja chica</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Caja</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>300.00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>300.00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>300.00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1.1.02.01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Banco Pichincha Cte. ***4521</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Banco</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>110000.00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>125680.50</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>131210.50</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>131210.50</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>1.1.02.02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Banco Guayaquil Aho. ***7788</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Banco</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>50000.00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>47700.00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>45900.00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>45900.00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>10000.00</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Garantía de préstamo (pignoración)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>30/06/2027</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>1.1.02.03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Produbanco Cte. ***3390</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Banco</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>20000.00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>22000.00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>22000.00</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>21500.00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>1.1.02.04</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Banco Internacional Cte. ***1102</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Banco</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>1500.00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1650.00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>1200.00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>1650.00</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Embargo judicial</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>1.1.02.05</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Banco Bolivariano Cte. ***5566</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Banco</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-2000.00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>-3200.00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>-3200.00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>-3200.00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>1.1.03.01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Póliza de acumulación Pichincha 60 días</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Inversión</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>50000.00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>50000.00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>50000.00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>50000.00</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>15/11/2025</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>14/01/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>1.1.03.02</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Certificado de depósito Produbanco 180 días</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Inversión</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>25000.00</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>01/10/2025</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
@@ -936,36 +1081,260 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>AuditConsulting Auditores Cía. Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Anexo de cuentas de caja, bancos e inversiones al corte</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Una fila por cuenta: código, banco/caja, tipo (Banco, Caja o Inversión), saldo según libros, saldo del estado bancario (o arqueo), saldo confirmado, restringido, monto, motivo y fin de la restricción; fechas de adquisición y vencimiento de inversiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa. Si su archivo usa otros nombres de columna, puede cargarlo igual: al procesar podrá mapear a mano dónde está cada dato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>EJEMPLO · datos ficticios</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anexo de cuentas de caja, bancos e inversiones al corte</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Una fila por cuenta: código, banco/caja, tipo (Banco, Caja o Inversión), saldo según libros, saldo del estado bancario (o arqueo), saldo confirmado, restringido, monto, motivo y fin de la restricción; fechas de adquisición y vencimiento de inversiones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Formato de ejemplo con datos ficticios que muestra la estructura esperada. La hoja «Datos» trae los rótulos que la prueba reconoce automáticamente; reemplace las filas por las de su empresa sin cambiar los encabezados.</t>
-        </is>
-      </c>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Obligatoria</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Qué va aquí (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Código de cuenta</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Banco / caja y número de cuenta</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Tipo (Banco, Caja o Inversión)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Saldo anterior (cierre previo)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Saldo según libros</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Saldo según estado bancario (o arqueo en caja)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Saldo confirmado por el banco</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Restringido (Sí/No)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Monto restringido</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Motivo de la restricción</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Fin de la restricción</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Restringido ya presentado aparte (Sí/No)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Fecha de adquisición (inversiones)</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Fecha de vencimiento (inversiones)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
